--- a/reports/QA_1200_Test_Executive_Report.xlsx
+++ b/reports/QA_1200_Test_Executive_Report.xlsx
@@ -548,7 +548,7 @@
         <v>300</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0</v>
@@ -557,11 +557,11 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -575,7 +575,7 @@
         <v>300</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="D6" s="4" t="n">
         <v>0</v>
@@ -584,11 +584,11 @@
         <v>0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -602,7 +602,7 @@
         <v>300</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="D7" s="4" t="n">
         <v>0</v>
@@ -611,11 +611,11 @@
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>2.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
         <v>300</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>6</v>
+        <v>300</v>
       </c>
       <c r="D8" s="4" t="n">
         <v>0</v>
@@ -638,11 +638,11 @@
         <v>0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>294</v>
+        <v>0</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
         <v>1200</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>27</v>
+        <v>1200</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
@@ -665,11 +665,11 @@
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1173</v>
+        <v>0</v>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>

--- a/reports/QA_1200_Test_Executive_Report.xlsx
+++ b/reports/QA_1200_Test_Executive_Report.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
@@ -754,6 +754,67 @@
         </is>
       </c>
     </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Data Quality Metrics</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Unique Test IDs</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>1200 / 1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Unique Test Names</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>1200 / 1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Unique Scenario Signatures</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>1200 / 1200</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Unique Complete Rows</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>1200 / 1200</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:G2"/>
